--- a/attachment/gmx/gmxmmpbsa_test.xlsx
+++ b/attachment/gmx/gmxmmpbsa_test.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\DDD\PBSA_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Git_PC\molakirlee.github.io\attachment\gmx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -93,7 +93,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -155,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -164,7 +164,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -300,32 +300,35 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>df!$A$2:$A$9</c:f>
+              <c:f>df!$A$2:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.14000000000000001</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>0.15</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>0.25</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>0.35</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>0.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -333,32 +336,35 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>df!$D$2:$D$9</c:f>
+              <c:f>df!$D$2:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>286.62599999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>286.95299999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>287.2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>287.62900000000002</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.000">
+                <c:pt idx="4" formatCode="0.000">
                   <c:v>290.16000000000003</c:v>
                 </c:pt>
-                <c:pt idx="4" formatCode="0.000">
+                <c:pt idx="5" formatCode="0.000">
                   <c:v>293.82799999999997</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="0.000">
+                <c:pt idx="6" formatCode="0.000">
                   <c:v>295.971</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0.000">
+                <c:pt idx="7" formatCode="0.000">
                   <c:v>300.274</c:v>
                 </c:pt>
-                <c:pt idx="7" formatCode="0.000">
+                <c:pt idx="8" formatCode="0.000">
                   <c:v>326.286</c:v>
                 </c:pt>
               </c:numCache>
@@ -374,11 +380,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="273606112"/>
-        <c:axId val="268788368"/>
+        <c:axId val="235587760"/>
+        <c:axId val="235587200"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="273606112"/>
+        <c:axId val="235587760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -435,12 +441,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="268788368"/>
+        <c:crossAx val="235587200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="268788368"/>
+        <c:axId val="235587200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -497,7 +503,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="273606112"/>
+        <c:crossAx val="235587760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -586,7 +592,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -718,11 +723,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="348333936"/>
-        <c:axId val="348331696"/>
+        <c:axId val="238968784"/>
+        <c:axId val="238969344"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="348333936"/>
+        <c:axId val="238968784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -779,12 +784,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="348331696"/>
+        <c:crossAx val="238969344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="348331696"/>
+        <c:axId val="238969344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -841,7 +846,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="348333936"/>
+        <c:crossAx val="238968784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1057,11 +1062,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="266339088"/>
-        <c:axId val="267745888"/>
+        <c:axId val="238971584"/>
+        <c:axId val="238972144"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="266339088"/>
+        <c:axId val="238971584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1118,12 +1123,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="267745888"/>
+        <c:crossAx val="238972144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="267745888"/>
+        <c:axId val="238972144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1180,7 +1185,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="266339088"/>
+        <c:crossAx val="238971584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2903,13 +2908,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>618451</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>95100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2941,13 +2946,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3021,13 +3026,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3519,7 +3524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
@@ -3609,16 +3614,16 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="B3">
-        <v>-215.69300000000001</v>
+        <v>-215.941</v>
       </c>
       <c r="C3">
         <v>-468.22699999999998</v>
       </c>
       <c r="D3" s="3">
-        <v>287.2</v>
+        <v>286.95299999999997</v>
       </c>
       <c r="E3">
         <v>-34.665999999999997</v>
@@ -3630,13 +3635,13 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J3">
-        <v>-5440.0640000000003</v>
+        <v>-5434.1880000000001</v>
       </c>
       <c r="K3">
-        <v>-5590.183</v>
+        <v>-5584.3509999999997</v>
       </c>
       <c r="L3">
-        <v>-137.08099999999999</v>
+        <v>-136.78899999999999</v>
       </c>
       <c r="N3">
         <v>229.666</v>
@@ -3650,16 +3655,16 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="3">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="B4">
-        <v>-215.26400000000001</v>
+        <v>-215.69300000000001</v>
       </c>
       <c r="C4">
         <v>-468.22699999999998</v>
       </c>
       <c r="D4" s="3">
-        <v>287.62900000000002</v>
+        <v>287.2</v>
       </c>
       <c r="E4">
         <v>-34.665999999999997</v>
@@ -3671,10 +3676,10 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J4">
-        <v>-5444.3559999999998</v>
+        <v>-5440.0640000000003</v>
       </c>
       <c r="K4">
-        <v>-5594.9040000000005</v>
+        <v>-5590.183</v>
       </c>
       <c r="L4">
         <v>-137.08099999999999</v>
@@ -3691,16 +3696,16 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="B5">
-        <v>-212.73400000000001</v>
+        <v>-215.26400000000001</v>
       </c>
       <c r="C5">
         <v>-468.22699999999998</v>
       </c>
-      <c r="D5" s="4">
-        <v>290.16000000000003</v>
+      <c r="D5" s="3">
+        <v>287.62900000000002</v>
       </c>
       <c r="E5">
         <v>-34.665999999999997</v>
@@ -3712,13 +3717,13 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J5">
-        <v>-5474.4260000000004</v>
+        <v>-5444.3559999999998</v>
       </c>
       <c r="K5">
-        <v>-5626.27</v>
+        <v>-5594.9040000000005</v>
       </c>
       <c r="L5">
-        <v>-138.316</v>
+        <v>-137.08099999999999</v>
       </c>
       <c r="N5">
         <v>229.666</v>
@@ -3732,16 +3737,16 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="B6">
-        <v>-209.066</v>
+        <v>-212.73400000000001</v>
       </c>
       <c r="C6">
         <v>-468.22699999999998</v>
       </c>
       <c r="D6" s="4">
-        <v>293.82799999999997</v>
+        <v>290.16000000000003</v>
       </c>
       <c r="E6">
         <v>-34.665999999999997</v>
@@ -3753,13 +3758,13 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J6">
-        <v>-5500.3990000000003</v>
+        <v>-5474.4260000000004</v>
       </c>
       <c r="K6">
-        <v>-5653.8940000000002</v>
+        <v>-5626.27</v>
       </c>
       <c r="L6">
-        <v>-140.33199999999999</v>
+        <v>-138.316</v>
       </c>
       <c r="N6">
         <v>229.666</v>
@@ -3773,16 +3778,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="B7">
-        <v>-206.923</v>
+        <v>-209.066</v>
       </c>
       <c r="C7">
         <v>-468.22699999999998</v>
       </c>
       <c r="D7" s="4">
-        <v>295.971</v>
+        <v>293.82799999999997</v>
       </c>
       <c r="E7">
         <v>-34.665999999999997</v>
@@ -3794,13 +3799,13 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J7">
-        <v>-5549.8370000000004</v>
+        <v>-5500.3990000000003</v>
       </c>
       <c r="K7">
-        <v>-5704.2349999999997</v>
+        <v>-5653.8940000000002</v>
       </c>
       <c r="L7">
-        <v>-141.57300000000001</v>
+        <v>-140.33199999999999</v>
       </c>
       <c r="N7">
         <v>229.666</v>
@@ -3814,16 +3819,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="B8">
-        <v>-202.62</v>
+        <v>-206.923</v>
       </c>
       <c r="C8">
         <v>-468.22699999999998</v>
       </c>
       <c r="D8" s="4">
-        <v>300.274</v>
+        <v>295.971</v>
       </c>
       <c r="E8">
         <v>-34.665999999999997</v>
@@ -3835,10 +3840,10 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J8">
-        <v>-5613.973</v>
+        <v>-5549.8370000000004</v>
       </c>
       <c r="K8">
-        <v>-5772.6729999999998</v>
+        <v>-5704.2349999999997</v>
       </c>
       <c r="L8">
         <v>-141.57300000000001</v>
@@ -3855,16 +3860,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="B9">
-        <v>-176.607</v>
+        <v>-202.62</v>
       </c>
       <c r="C9">
         <v>-468.22699999999998</v>
       </c>
       <c r="D9" s="4">
-        <v>326.286</v>
+        <v>300.274</v>
       </c>
       <c r="E9">
         <v>-34.665999999999997</v>
@@ -3876,13 +3881,13 @@
         <v>-321.06900000000002</v>
       </c>
       <c r="J9">
-        <v>-5758.1490000000003</v>
+        <v>-5613.973</v>
       </c>
       <c r="K9">
-        <v>-5923.2780000000002</v>
+        <v>-5772.6729999999998</v>
       </c>
       <c r="L9">
-        <v>-161.15799999999999</v>
+        <v>-141.57300000000001</v>
       </c>
       <c r="N9">
         <v>229.666</v>
@@ -3895,12 +3900,50 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1"/>
+      <c r="A10" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B10">
+        <v>-176.607</v>
+      </c>
+      <c r="C10">
+        <v>-468.22699999999998</v>
+      </c>
+      <c r="D10" s="4">
+        <v>326.286</v>
+      </c>
+      <c r="E10">
+        <v>-34.665999999999997</v>
+      </c>
+      <c r="G10">
+        <v>-147.15799999999999</v>
+      </c>
+      <c r="H10">
+        <v>-321.06900000000002</v>
+      </c>
+      <c r="J10">
+        <v>-5758.1490000000003</v>
+      </c>
+      <c r="K10">
+        <v>-5923.2780000000002</v>
+      </c>
+      <c r="L10">
+        <v>-161.15799999999999</v>
+      </c>
+      <c r="N10">
+        <v>229.666</v>
+      </c>
+      <c r="O10">
+        <v>239.744</v>
+      </c>
+      <c r="P10">
+        <v>24.588000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
@@ -3942,6 +3985,9 @@
     <row r="24" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D24" s="1"/>
     </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D25" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
